--- a/reports/bug_report.xlsx
+++ b/reports/bug_report.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -971,11 +971,11 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 12:00</t>
+          <t>2026-10-13 12:04</t>
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 12:00</t>
+          <t>2026-10-13 12:04</t>
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr">
@@ -1757,11 +1757,11 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 12:00</t>
+          <t>2026-10-13 12:04</t>
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr">
@@ -1826,11 +1826,11 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 12:00</t>
+          <t>2026-10-13 12:04</t>
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr">
@@ -1895,11 +1895,11 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 12:00</t>
+          <t>2026-10-13 12:04</t>
         </is>
       </c>
       <c r="O18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr">
@@ -1964,11 +1964,11 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 12:00</t>
+          <t>2026-10-13 12:04</t>
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr">
@@ -2033,11 +2033,11 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 12:00</t>
+          <t>2026-10-13 12:04</t>
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Riyadh, Saudi Arabia -&gt; N'guigmi, Niger</t>
+          <t>Long Beach, United States -&gt; Dammam, Saudi Arabia</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>no price at add (ppd_amount=None) (partner had quoted amount 885.04)</t>
+          <t>NO PRICE (ppd_amount=None) (quoted 550.55)</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>booking_id 6acdd0104283fe863f021256; .auth/debug_create_parcel_booking_response.json</t>
+          <t>probe: reports/partner_probe.csv</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2195,11 +2195,11 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 12:00</t>
+          <t>2026-10-13 12:04</t>
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr">
@@ -2286,6 +2286,249 @@
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>quoted_but_unpriced_at_add|parcel|dhl_express_worldwide</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>BUG-023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Partner with a quote is priced 0/null by /bookings/add</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Suspected - verify in UI</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>POST /bookings/add</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>parcel</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>fedex_priority</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Long Beach, United States -&gt; Dammam, Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Partner quoted by get_delivery_and_rate gets a real price at /bookings/add.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>NO PRICE (ppd_amount=None) (quoted 738.65)</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>probe: reports/partner_probe.csv</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:04</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:04</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>quoted_but_unpriced_at_add|parcel|fedex_priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>BUG-024</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Partner with a quote is priced 0/null by /bookings/add</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Suspected - verify in UI</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>POST /bookings/add</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>parcel</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>fedex_connect_plus</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Long Beach, United States -&gt; Dammam, Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Partner quoted by get_delivery_and_rate gets a real price at /bookings/add.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>NO PRICE (ppd_amount=None) (quoted 3903.84)</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>probe: reports/partner_probe.csv</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:04</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:04</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>quoted_but_unpriced_at_add|parcel|fedex_connect_plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>BUG-025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Partner with a quote is priced 0/null by /bookings/add</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Suspected - verify in UI</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>POST /bookings/add</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>pallet</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>aramex</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>ابها, Saudi Arabia -&gt; Gerlos, Austria</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Partner quoted by get_delivery_and_rate gets a real price at /bookings/add.</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>NO PRICE (ppd_amount=0) (quoted 5573.7)</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>probe: reports/partner_probe.csv</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:04</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:04</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>quoted_but_unpriced_at_add|pallet|aramex</t>
         </is>
       </c>
     </row>
